--- a/data/trans_orig/P33_1_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62968</t>
+          <t>61279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>96153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>91581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>129021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180494</t>
+          <t>177968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172686</t>
+          <t>169609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222087</t>
+          <t>220066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344296</t>
+          <t>346612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>409852</t>
+          <t>410287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>529536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>616607</t>
+          <t>612648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>717319</t>
+          <t>715849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>771320</t>
+          <t>770460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>825141</t>
+          <t>821955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>892411</t>
+          <t>888029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1560688</t>
+          <t>1558857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1650592</t>
+          <t>1648372</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37752</t>
+          <t>35368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63919</t>
+          <t>61926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75311</t>
+          <t>76944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114043</t>
+          <t>116677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163663</t>
+          <t>163834</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215742</t>
+          <t>215426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>203712</t>
+          <t>206045</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>257718</t>
+          <t>262068</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>380875</t>
+          <t>382741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>456869</t>
+          <t>462793</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1402161</t>
+          <t>1402471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1458918</t>
+          <t>1460850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1262784</t>
+          <t>1260626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1323333</t>
+          <t>1320486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2683318</t>
+          <t>2680751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2767718</t>
+          <t>2764951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16155</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>39036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58470</t>
+          <t>57038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90870</t>
+          <t>90653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56238</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84448</t>
+          <t>86468</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123123</t>
+          <t>121777</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168321</t>
+          <t>165394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436532</t>
+          <t>436200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>470745</t>
+          <t>472008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379756</t>
+          <t>379505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410821</t>
+          <t>411829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>825707</t>
+          <t>828307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>875693</t>
+          <t>873958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119005</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165359</t>
+          <t>163163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107077</t>
+          <t>108510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153221</t>
+          <t>153480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238714</t>
+          <t>238600</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303546</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417884</t>
+          <t>419514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498886</t>
+          <t>500762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>628010</t>
+          <t>630708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>723669</t>
+          <t>722399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074562</t>
+          <t>1073329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1195232</t>
+          <t>1192458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2588708</t>
+          <t>2582930</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2674029</t>
+          <t>2674378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2501367</t>
+          <t>2498276</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2598566</t>
+          <t>2596209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5118185</t>
+          <t>5112156</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5248700</t>
+          <t>5243770</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96803</t>
+          <t>98908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138889</t>
+          <t>142582</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>96907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141304</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206664</t>
+          <t>202988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269291</t>
+          <t>266660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191399</t>
+          <t>191729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244905</t>
+          <t>242948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424863</t>
+          <t>424811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497959</t>
+          <t>496583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>634267</t>
+          <t>635319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>725965</t>
+          <t>725271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>604121</t>
+          <t>598836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>663796</t>
+          <t>663580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>717008</t>
+          <t>720591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>791135</t>
+          <t>793971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1338750</t>
+          <t>1342535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1435513</t>
+          <t>1434820</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53798</t>
+          <t>52810</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85905</t>
+          <t>85155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>41336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70796</t>
+          <t>72607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101180</t>
+          <t>100538</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146055</t>
+          <t>147206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>331612</t>
+          <t>336573</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>403835</t>
+          <t>404824</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>398317</t>
+          <t>398850</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>474548</t>
+          <t>471803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>752428</t>
+          <t>745723</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>858564</t>
+          <t>855433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1479928</t>
+          <t>1481020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1557704</t>
+          <t>1555293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1225551</t>
+          <t>1225393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1303776</t>
+          <t>1302014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2724999</t>
+          <t>2725328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2837037</t>
+          <t>2842446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>27276</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84268</t>
+          <t>84446</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122023</t>
+          <t>123145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>60533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94861</t>
+          <t>94013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154430</t>
+          <t>155201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205004</t>
+          <t>204508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>351939</t>
+          <t>350139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>390974</t>
+          <t>389777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355168</t>
+          <t>353969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387278</t>
+          <t>390212</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>719127</t>
+          <t>719092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>770515</t>
+          <t>770383</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>163875</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226648</t>
+          <t>222149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154875</t>
+          <t>156418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209283</t>
+          <t>211743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338369</t>
+          <t>340777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>418532</t>
+          <t>416272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>639460</t>
+          <t>637866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>731985</t>
+          <t>734067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>915945</t>
+          <t>920323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1022114</t>
+          <t>1025604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1587869</t>
+          <t>1584464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1734290</t>
+          <t>1737165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2470376</t>
+          <t>2474890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2577049</t>
+          <t>2581412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2336731</t>
+          <t>2333200</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2442970</t>
+          <t>2445622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4834427</t>
+          <t>4835130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4998194</t>
+          <t>5000791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68188</t>
+          <t>69810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102809</t>
+          <t>102787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68459</t>
+          <t>69160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106234</t>
+          <t>108196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>145989</t>
+          <t>148470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199034</t>
+          <t>198565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117878</t>
+          <t>118983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159583</t>
+          <t>160277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281534</t>
+          <t>275883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339865</t>
+          <t>338899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>407007</t>
+          <t>409752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486560</t>
+          <t>486575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505445</t>
+          <t>503990</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>552574</t>
+          <t>552436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>556060</t>
+          <t>560160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>619792</t>
+          <t>625834</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1079398</t>
+          <t>1078417</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1163011</t>
+          <t>1157105</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>66118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106404</t>
+          <t>104479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51524</t>
+          <t>53110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87048</t>
+          <t>86132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>129985</t>
+          <t>130484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178987</t>
+          <t>179935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>327063</t>
+          <t>326815</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399206</t>
+          <t>396426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>388391</t>
+          <t>389323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>467502</t>
+          <t>461582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>733525</t>
+          <t>736580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>838602</t>
+          <t>845076</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1586146</t>
+          <t>1583051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1662305</t>
+          <t>1658541</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1445813</t>
+          <t>1450476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1526412</t>
+          <t>1526268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3059583</t>
+          <t>3052811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3169142</t>
+          <t>3168567</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22151</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>82593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123544</t>
+          <t>121360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88899</t>
+          <t>90712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128565</t>
+          <t>127740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182128</t>
+          <t>183601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237366</t>
+          <t>236012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>408391</t>
+          <t>412760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451949</t>
+          <t>453189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411459</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451704</t>
+          <t>450312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836891</t>
+          <t>836189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893101</t>
+          <t>888312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157915</t>
+          <t>160870</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211101</t>
+          <t>209994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138940</t>
+          <t>139042</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190537</t>
+          <t>192873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308589</t>
+          <t>308389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>381663</t>
+          <t>384588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554544</t>
+          <t>555835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646215</t>
+          <t>647094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>791846</t>
+          <t>787202</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>892890</t>
+          <t>891828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1366428</t>
+          <t>1371679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1509373</t>
+          <t>1519492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2538860</t>
+          <t>2535032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2637967</t>
+          <t>2633441</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2462005</t>
+          <t>2457747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2570547</t>
+          <t>2573138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5029752</t>
+          <t>5023181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5186334</t>
+          <t>5177445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,16%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023</t>
+          <t>Población según si duerme más, menos o las horas de sueño recomendadas por la Sociedad Española del Sueño en 2023 (tasa de respuesta: 97,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33189</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>50426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76666</t>
+          <t>76571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126525</t>
+          <t>126782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162591</t>
+          <t>162356</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230616</t>
+          <t>230102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268833</t>
+          <t>269852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367826</t>
+          <t>366132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419211</t>
+          <t>420010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311994</t>
+          <t>313265</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>350991</t>
+          <t>350918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413669</t>
+          <t>411879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>452286</t>
+          <t>450684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>736454</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>790178</t>
+          <t>792333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>43773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284198</t>
+          <t>274524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>509333</t>
+          <t>511465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>538071</t>
+          <t>530967</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1098206</t>
+          <t>1105062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>936426</t>
+          <t>943687</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1599035</t>
+          <t>1670484</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1680146</t>
+          <t>1679512</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1918211</t>
+          <t>1925836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1059103</t>
+          <t>1054759</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1607844</t>
+          <t>1612874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2746093</t>
+          <t>2687633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3401234</t>
+          <t>3398512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121768</t>
+          <t>121935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178105</t>
+          <t>178862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>149503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192223</t>
+          <t>188213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284518</t>
+          <t>284162</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352254</t>
+          <t>350543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>455926</t>
+          <t>457727</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>512881</t>
+          <t>513229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451877</t>
+          <t>453138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494257</t>
+          <t>493058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>927135</t>
+          <t>927677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>993691</t>
+          <t>992982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31883</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60559</t>
+          <t>60171</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>63424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99216</t>
+          <t>99947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106101</t>
+          <t>103561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147723</t>
+          <t>147700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>542750</t>
+          <t>574095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>808384</t>
+          <t>801454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>955701</t>
+          <t>963072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1577920</t>
+          <t>1646004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,47 +8429,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>27,12%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>46,35%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2489</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1856644</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1644494</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2389074</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>26,91%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2489</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1856644</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1654024</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2347432</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2492358</t>
+          <t>2497232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2777745</t>
+          <t>2742721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1895744</t>
+          <t>1837181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2509408</t>
+          <t>2499740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4435516</t>
+          <t>4436756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5119581</t>
+          <t>5134466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61279</t>
+          <t>62682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>95765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56771</t>
+          <t>57426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91581</t>
+          <t>90775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129021</t>
+          <t>129776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177968</t>
+          <t>177960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169609</t>
+          <t>172830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>220066</t>
+          <t>221387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>346612</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>410287</t>
+          <t>409486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529536</t>
+          <t>531793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612648</t>
+          <t>616341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>715849</t>
+          <t>715556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>770460</t>
+          <t>772268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>821955</t>
+          <t>826731</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>888029</t>
+          <t>894086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1558857</t>
+          <t>1555180</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1648372</t>
+          <t>1649059</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>32914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60926</t>
+          <t>60207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>36270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61926</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76944</t>
+          <t>75551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116677</t>
+          <t>112779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163834</t>
+          <t>165291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215426</t>
+          <t>221101</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,82 +1317,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>230459</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>205400</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>257306</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>419145</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>383399</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>460428</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>12,94%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>230459</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>206045</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>262068</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>419145</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>382741</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>462793</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1402471</t>
+          <t>1398735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1460850</t>
+          <t>1456744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1260626</t>
+          <t>1263287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1320486</t>
+          <t>1322950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2680751</t>
+          <t>2680425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2764951</t>
+          <t>2766418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39036</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>58038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90653</t>
+          <t>92015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86468</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121777</t>
+          <t>121735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165394</t>
+          <t>169661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436200</t>
+          <t>436085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472008</t>
+          <t>472536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379505</t>
+          <t>379468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>411829</t>
+          <t>410916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>828307</t>
+          <t>823938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>873958</t>
+          <t>875640</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117421</t>
+          <t>120409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163163</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108510</t>
+          <t>109096</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153480</t>
+          <t>155579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>241568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>305462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419514</t>
+          <t>419409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500762</t>
+          <t>503270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>630708</t>
+          <t>633559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722399</t>
+          <t>730030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1073329</t>
+          <t>1075370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192458</t>
+          <t>1196163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2582930</t>
+          <t>2579842</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2674378</t>
+          <t>2675558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2498276</t>
+          <t>2496057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2596209</t>
+          <t>2595772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5112156</t>
+          <t>5117800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5243770</t>
+          <t>5248057</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98908</t>
+          <t>97457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142582</t>
+          <t>142130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96907</t>
+          <t>98098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139267</t>
+          <t>142014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>202988</t>
+          <t>205709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266660</t>
+          <t>269783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191729</t>
+          <t>191743</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>242948</t>
+          <t>244488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424811</t>
+          <t>424754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>496583</t>
+          <t>499779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>635319</t>
+          <t>635185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>725271</t>
+          <t>725702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>598836</t>
+          <t>601460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>663580</t>
+          <t>663947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>720591</t>
+          <t>714857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>793971</t>
+          <t>792522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1342535</t>
+          <t>1339992</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1434820</t>
+          <t>1439009</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,46%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52810</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85155</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>39191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72607</t>
+          <t>69933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100538</t>
+          <t>99366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147206</t>
+          <t>144051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>336573</t>
+          <t>333733</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>404824</t>
+          <t>407385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>398850</t>
+          <t>401183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>471803</t>
+          <t>469473</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>745723</t>
+          <t>747643</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>855433</t>
+          <t>856884</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1481020</t>
+          <t>1478869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1555293</t>
+          <t>1556699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1225393</t>
+          <t>1226502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1302014</t>
+          <t>1300938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2725328</t>
+          <t>2725417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2842446</t>
+          <t>2841073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>82397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123145</t>
+          <t>120885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60533</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>93941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155201</t>
+          <t>155780</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204508</t>
+          <t>207183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350139</t>
+          <t>351732</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>389777</t>
+          <t>391761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353969</t>
+          <t>353359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>390212</t>
+          <t>388054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>719092</t>
+          <t>715528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>770383</t>
+          <t>769090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163875</t>
+          <t>165185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>222149</t>
+          <t>225544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156418</t>
+          <t>153162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211743</t>
+          <t>208814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>340777</t>
+          <t>336871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416272</t>
+          <t>412809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>637866</t>
+          <t>641183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>734067</t>
+          <t>736135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>920323</t>
+          <t>917171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1025604</t>
+          <t>1027547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1584464</t>
+          <t>1590079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1737165</t>
+          <t>1741085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2474890</t>
+          <t>2468881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2581412</t>
+          <t>2572878</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2333200</t>
+          <t>2331898</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2445622</t>
+          <t>2449052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4835130</t>
+          <t>4830865</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5000791</t>
+          <t>4986472</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69810</t>
+          <t>68896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102787</t>
+          <t>104159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69160</t>
+          <t>66413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108196</t>
+          <t>107118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148470</t>
+          <t>149150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198565</t>
+          <t>198044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118983</t>
+          <t>117185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160277</t>
+          <t>160121</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275883</t>
+          <t>281034</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338899</t>
+          <t>341151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409752</t>
+          <t>410777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>486575</t>
+          <t>486699</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503990</t>
+          <t>503832</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>552436</t>
+          <t>553954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>560160</t>
+          <t>556431</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>625834</t>
+          <t>622795</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1078417</t>
+          <t>1078776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1157105</t>
+          <t>1160980</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66118</t>
+          <t>67582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104479</t>
+          <t>103555</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,82 +5314,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54027</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>86694</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>153260</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>129367</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>181471</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>68583</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53110</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86132</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>153260</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>130484</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>179935</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>326815</t>
+          <t>328164</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>396426</t>
+          <t>396906</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>389323</t>
+          <t>385799</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>461582</t>
+          <t>465178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>736580</t>
+          <t>731305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>845076</t>
+          <t>836296</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1583051</t>
+          <t>1585382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1658541</t>
+          <t>1664064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1450476</t>
+          <t>1443547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1526268</t>
+          <t>1526597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3052811</t>
+          <t>3060000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3168567</t>
+          <t>3169002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16518</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33008</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82593</t>
+          <t>81426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>121360</t>
+          <t>120758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90712</t>
+          <t>90604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127740</t>
+          <t>129375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183601</t>
+          <t>184044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236012</t>
+          <t>237810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>411832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453189</t>
+          <t>452763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>410840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450312</t>
+          <t>450403</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836189</t>
+          <t>836075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>888312</t>
+          <t>892491</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>160870</t>
+          <t>156920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209994</t>
+          <t>209775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139042</t>
+          <t>139103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>192873</t>
+          <t>192339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>308389</t>
+          <t>310537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384588</t>
+          <t>384344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>555835</t>
+          <t>556704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>647094</t>
+          <t>650731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>787202</t>
+          <t>794622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>891828</t>
+          <t>891518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1371679</t>
+          <t>1364286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1519492</t>
+          <t>1507014</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2535032</t>
+          <t>2542270</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2633441</t>
+          <t>2637158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2457747</t>
+          <t>2461367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2573138</t>
+          <t>2568423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5023181</t>
+          <t>5033731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5177445</t>
+          <t>5171633</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50426</t>
+          <t>54161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>67348</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50722</t>
+          <t>54700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76571</t>
+          <t>83330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>143255</t>
+          <t>155565</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126782</t>
+          <t>135617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162356</t>
+          <t>174071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>250028</t>
+          <t>271336</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>230102</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269852</t>
+          <t>290794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>393283</t>
+          <t>426900</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366132</t>
+          <t>399258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>420010</t>
+          <t>456804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332348</t>
+          <t>379775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>313265</t>
+          <t>359255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>350918</t>
+          <t>399716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>431794</t>
+          <t>473227</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>411879</t>
+          <t>451085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>450684</t>
+          <t>494334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>764142</t>
+          <t>853001</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>818959</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>792333</t>
+          <t>883355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,57%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>499746</t>
+          <t>561249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>720987</t>
+          <t>786001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1220734</t>
+          <t>1347250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43773</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48747</t>
+          <t>59154</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>74972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>438874</t>
+          <t>479529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>274524</t>
+          <t>442585</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511465</t>
+          <t>522694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>709171</t>
+          <t>559750</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>530967</t>
+          <t>525033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1105062</t>
+          <t>596723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1148044</t>
+          <t>1039280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>943687</t>
+          <t>982913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1670484</t>
+          <t>1096697</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1754258</t>
+          <t>1653422</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1679512</t>
+          <t>1610353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1925836</t>
+          <t>1691870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1435570</t>
+          <t>1505228</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1054759</t>
+          <t>1468393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1612874</t>
+          <t>1542559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3189827</t>
+          <t>3158650</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2687633</t>
+          <t>3101957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3398512</t>
+          <t>3217435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2210901</t>
+          <t>2153607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2175718</t>
+          <t>2103476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4386618</t>
+          <t>4257084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19986</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>152699</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121935</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178862</t>
+          <t>178080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>168965</t>
+          <t>187637</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149503</t>
+          <t>167784</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188213</t>
+          <t>208462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>315316</t>
+          <t>340336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>284162</t>
+          <t>306709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>350543</t>
+          <t>371323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>488381</t>
+          <t>544408</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457727</t>
+          <t>518901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513229</t>
+          <t>567421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>473788</t>
+          <t>527390</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>453138</t>
+          <t>504529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493058</t>
+          <t>548298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>962168</t>
+          <t>1071798</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>927677</t>
+          <t>1038073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>992982</t>
+          <t>1104979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>638304</t>
+          <t>701549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>728049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1292519</t>
+          <t>1429598</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45483</t>
+          <t>51007</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60171</t>
+          <t>65934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>81607</t>
+          <t>92960</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>77657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99947</t>
+          <t>112637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>127090</t>
+          <t>143967</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103561</t>
+          <t>122378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147700</t>
+          <t>166492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>728481</t>
+          <t>787794</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>574095</t>
+          <t>732900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>801454</t>
+          <t>839039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1128162</t>
+          <t>1018722</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>963072</t>
+          <t>972663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1646004</t>
+          <t>1065641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1856644</t>
+          <t>1806516</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1644494</t>
+          <t>1736133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2389074</t>
+          <t>1870059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2574986</t>
+          <t>2577605</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2497232</t>
+          <t>2524866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2742721</t>
+          <t>2632976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2341151</t>
+          <t>2505844</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1837181</t>
+          <t>2460917</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2499740</t>
+          <t>2557318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4916137</t>
+          <t>5083449</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4436756</t>
+          <t>5017040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5134466</t>
+          <t>5156933</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3348951</t>
+          <t>3416406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3550920</t>
+          <t>3617526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6899871</t>
+          <t>7033932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
